--- a/outputs/实际生产状态表_四宽度混合核对.xlsx
+++ b/outputs/实际生产状态表_四宽度混合核对.xlsx
@@ -12463,8 +12463,16 @@
           <t>检查失败原因并人工复核后重新排版</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1500\G004_single_spec_cutting_plan.png</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1500\G004_single_spec_cutting_report.txt</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>已比较 4 个直排候选方案</t>
@@ -12923,8 +12931,16 @@
           <t>检查失败原因并人工复核后重新排版</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1250\G009_single_spec_cutting_plan.png</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1250\G009_single_spec_cutting_report.txt</t>
+        </is>
+      </c>
       <c r="X10" t="inlineStr">
         <is>
           <t>已比较 6 个直排候选方案</t>
@@ -13195,8 +13211,16 @@
           <t>检查失败原因并人工复核后重新排版</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1240\G012_single_spec_cutting_plan.png</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1240\G012_single_spec_cutting_report.txt</t>
+        </is>
+      </c>
       <c r="X13" t="inlineStr">
         <is>
           <t>已比较 8 个直排候选方案</t>
@@ -13279,8 +13303,16 @@
           <t>检查失败原因并人工复核后重新排版</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1000\G013_single_spec_cutting_plan.png</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1000\G013_single_spec_cutting_report.txt</t>
+        </is>
+      </c>
       <c r="X14" t="inlineStr">
         <is>
           <t>已比较 8 个直排候选方案</t>
@@ -13363,8 +13395,16 @@
           <t>检查失败原因并人工复核后重新排版</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1240\G014_single_spec_cutting_plan.png</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1240\G014_single_spec_cutting_report.txt</t>
+        </is>
+      </c>
       <c r="X15" t="inlineStr">
         <is>
           <t>已比较 7 个直排候选方案</t>
@@ -13447,8 +13487,16 @@
           <t>检查失败原因并人工复核后重新排版</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1250\G015_single_spec_cutting_plan.png</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1250\G015_single_spec_cutting_report.txt</t>
+        </is>
+      </c>
       <c r="X16" t="inlineStr">
         <is>
           <t>已比较 6 个直排候选方案</t>
@@ -13531,8 +13579,16 @@
           <t>检查失败原因并人工复核后重新排版</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1240\G016_single_spec_cutting_plan.png</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1240\G016_single_spec_cutting_report.txt</t>
+        </is>
+      </c>
       <c r="X17" t="inlineStr">
         <is>
           <t>已比较 3 个直排候选方案</t>
@@ -13615,8 +13671,16 @@
           <t>检查失败原因并人工复核后重新排版</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1240\G017_single_spec_cutting_plan.png</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1240\G017_single_spec_cutting_report.txt</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr">
         <is>
           <t>已比较 8 个直排候选方案</t>
@@ -13699,8 +13763,16 @@
           <t>检查失败原因并人工复核后重新排版</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1240\G018_single_spec_cutting_plan.png</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1240\G018_single_spec_cutting_report.txt</t>
+        </is>
+      </c>
       <c r="X19" t="inlineStr">
         <is>
           <t>已比较 3 个直排候选方案</t>
@@ -13971,8 +14043,16 @@
           <t>检查失败原因并人工复核后重新排版</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1250\G021_single_spec_cutting_plan.png</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1250\G021_single_spec_cutting_report.txt</t>
+        </is>
+      </c>
       <c r="X22" t="inlineStr">
         <is>
           <t>已比较 6 个直排候选方案</t>
@@ -14129,8 +14209,16 @@
           <t>检查失败原因并人工复核后重新排版</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1500\G023_single_spec_cutting_plan.png</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1500\G023_single_spec_cutting_report.txt</t>
+        </is>
+      </c>
       <c r="X24" t="inlineStr">
         <is>
           <t>已比较 5 个直排候选方案</t>
@@ -14213,8 +14301,16 @@
           <t>检查失败原因并人工复核后重新排版</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1240\G024_single_spec_cutting_plan.png</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1240\G024_single_spec_cutting_report.txt</t>
+        </is>
+      </c>
       <c r="X25" t="inlineStr">
         <is>
           <t>已比较 4 个直排候选方案</t>
@@ -14673,8 +14769,16 @@
           <t>检查失败原因并人工复核后重新排版</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1250\G029_single_spec_cutting_plan.png</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1250\G029_single_spec_cutting_report.txt</t>
+        </is>
+      </c>
       <c r="X30" t="inlineStr">
         <is>
           <t>已比较 2 个直排候选方案</t>
@@ -14757,8 +14861,16 @@
           <t>检查失败原因并人工复核后重新排版</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1240\G030_single_spec_cutting_plan.png</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1240\G030_single_spec_cutting_report.txt</t>
+        </is>
+      </c>
       <c r="X31" t="inlineStr">
         <is>
           <t>已比较 7 个直排候选方案</t>
@@ -14935,8 +15047,16 @@
           <t>检查失败原因并人工复核后重新排版</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1250\G032_single_spec_cutting_plan.png</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1250\G032_single_spec_cutting_report.txt</t>
+        </is>
+      </c>
       <c r="X33" t="inlineStr">
         <is>
           <t>已比较 6 个直排候选方案</t>
@@ -15019,8 +15139,16 @@
           <t>检查失败原因并人工复核后重新排版</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1500\G033_single_spec_cutting_plan.png</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1500\G033_single_spec_cutting_report.txt</t>
+        </is>
+      </c>
       <c r="X34" t="inlineStr">
         <is>
           <t>已比较 7 个直排候选方案</t>
@@ -15197,8 +15325,16 @@
           <t>检查失败原因并人工复核后重新排版</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1250\G035_single_spec_cutting_plan.png</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1250\G035_single_spec_cutting_report.txt</t>
+        </is>
+      </c>
       <c r="X36" t="inlineStr">
         <is>
           <t>已比较 6 个直排候选方案</t>
@@ -15657,8 +15793,16 @@
           <t>检查失败原因并人工复核后重新排版</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1240\G040_single_spec_cutting_plan.png</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1240\G040_single_spec_cutting_report.txt</t>
+        </is>
+      </c>
       <c r="X41" t="inlineStr">
         <is>
           <t>已比较 4 个直排候选方案</t>
@@ -15741,8 +15885,16 @@
           <t>检查失败原因并人工复核后重新排版</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1500\G041_single_spec_cutting_plan.png</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1500\G041_single_spec_cutting_report.txt</t>
+        </is>
+      </c>
       <c r="X42" t="inlineStr">
         <is>
           <t>已比较 8 个直排候选方案</t>
@@ -15825,8 +15977,16 @@
           <t>检查失败原因并人工复核后重新排版</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1240\G042_single_spec_cutting_plan.png</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>outputs\actual_production_runs\mixed_width_full_check\width_1240\G042_single_spec_cutting_report.txt</t>
+        </is>
+      </c>
       <c r="X43" t="inlineStr">
         <is>
           <t>已比较 3 个直排候选方案</t>
